--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +918,113 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128761180</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100779</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedgölen, Smedgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>543447</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6446396</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tjärstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129085224</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41583-2025 artfynd.xlsx
+++ b/artfynd/A 41583-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>128761180</v>
       </c>
       <c r="B4" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>129085224</v>
       </c>
       <c r="B5" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
